--- a/output/2026-10-05_23_Croazia_Međimurska_ATEX_Equipment-Services.xlsx
+++ b/output/2026-10-05_23_Croazia_Međimurska_ATEX_Equipment-Services.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Distributore locale di componenti elettrici/elettronici a Čakovec (Uska 1). Sito ufficiale verificato via fetch: conferma presenza linea "ATEX svjetiljke" (lampade/torce antideflagranti) nella sezione illuminazione a batteria, oltre a materiale elettrico, strumenti di misura, cavi e connettori.</t>
+          <t>Distributore locale di componenti elettrici/elettronici a Čakovec (Uska 1). Sito ufficiale verificato via fetch: conferma presenza linea "ATEX svjetiljke" (lampade/torce antideflagranti) nella sezione illuminazione a batteria, oltre a materiale elettrico, strumenti di misura, cavi e connettori. [DUPLICATO — vedi anche: 2026-09-20_09_Croazia_Vukovarsko-srijemska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -526,7 +526,6 @@
           <t>Elpro Solutions d.o.o.</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Zagreb - copertura nazionale Croazia (incl. Međimurska županija)</t>
@@ -537,8 +536,6 @@
           <t>ATEX Equipment/Services</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Distributore esclusivo per la Croazia di Pepperl+Fuchs e VEGA Grieshaber KG: dispositivi certificati Ex, barriere galvaniche, sistemi di pressurizzazione per aree pericolose. Indirizzo: Vinkovačka ulica 24, 10110 Zagreb. Esistenza confermata tramite profilo aziendale su automa.net (risultati ricerca web, pagina non accessibile in fetch diretto - 403); sito web proprio, telefono ed email non reperiti/verificabili, campi lasciati vuoti.</t>
@@ -583,7 +580,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Organismo notificato UE n. 2829 per certificazione ATEX (Direttiva 2014/34/UE) e IECEx (ExCB/ExTL), succeduto a Ex-Agencija; laboratorio accreditato ISO/IEC 17025 per prove su apparecchiature destinate ad atmosfere esplosive. Non è un rivenditore di prodotti ma un partner di certificazione/testing per il settore ATEX. Verificato tramite ricerca web (documentazione IECEx ufficiale).</t>
+          <t>Organismo notificato UE n. 2829 per certificazione ATEX (Direttiva 2014/34/UE) e IECEx (ExCB/ExTL), succeduto a Ex-Agencija; laboratorio accreditato ISO/IEC 17025 per prove su apparecchiature destinate ad atmosfere esplosive. Non è un rivenditore di prodotti ma un partner di certificazione/testing per il settore ATEX. Verificato tramite ricerca web (documentazione IECEx ufficiale). [DUPLICATO — vedi anche: 2026-09-13_02_Croazia_Varazdinska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
